--- a/P09Facility/src/test/resources/testdata/IlpnInventoryData.xlsx
+++ b/P09Facility/src/test/resources/testdata/IlpnInventoryData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500"/>
+    <workbookView windowWidth="19635" windowHeight="6900"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
   <si>
     <t>IlpnId</t>
   </si>
@@ -41,16 +41,43 @@
     <t>Location</t>
   </si>
   <si>
+    <t>LPN24092641823</t>
+  </si>
+  <si>
     <t>190_Cheese_blocks_100g</t>
   </si>
   <si>
     <t>190R1011</t>
   </si>
   <si>
+    <t>LPN24092675902</t>
+  </si>
+  <si>
+    <t>190_Coffee_maker_2Kg</t>
+  </si>
+  <si>
     <t>190R7051</t>
   </si>
   <si>
-    <t>190_Coffee_maker_2Kg</t>
+    <t>LPN24092623415</t>
+  </si>
+  <si>
+    <t>LPN24092689104</t>
+  </si>
+  <si>
+    <t>LPN24092634589</t>
+  </si>
+  <si>
+    <t>LPN24092661278</t>
+  </si>
+  <si>
+    <t>LPN24092693845</t>
+  </si>
+  <si>
+    <t>LPN24092615673</t>
+  </si>
+  <si>
+    <t>LPN24092654901</t>
   </si>
 </sst>
 </file>
@@ -63,7 +90,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +105,12 @@
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -542,150 +575,154 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1025,11 +1062,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="10.375" customWidth="1"/>
-    <col min="2" max="2" width="19.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="18.875" customWidth="1"/>
+    <col min="2" max="2" width="22.375" customWidth="1"/>
     <col min="3" max="3" width="7.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1047,74 +1084,130 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="28.5" spans="1:4">
-      <c r="A2" s="3">
-        <v>9692171121</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4">
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5">
         <v>180</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" ht="28.5" spans="1:4">
-      <c r="A3" s="3">
-        <v>9692182121</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4">
-        <v>200</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5">
+        <v>120</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" ht="28.5" spans="1:4">
-      <c r="A4" s="3">
-        <v>9692193121</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4">
-        <v>150</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5">
+        <v>120</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="5" ht="28.5" spans="1:4">
-      <c r="A5" s="3">
-        <v>9692204121</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4">
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="5">
         <v>120</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
+      <c r="D5" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="3">
-        <v>9692204141</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5">
         <v>120</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
+      <c r="D6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5">
+        <v>120</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5">
+        <v>120</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5">
+        <v>120</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>120</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
